--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED15.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED15.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>209W</t>
+          <t>196W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L5"/>
+  <dimension ref="B2:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1697,116 +1697,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-2-0110</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>133W</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>第2年</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0季</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>第3年3季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0004</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>80W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第4年3季</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
@@ -1821,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G53"/>
+  <dimension ref="B2:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2371,14 +2261,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-48</v>
+        <v>-4</v>
       </c>
       <c r="E23" t="n">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2277,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2397,14 +2287,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2303,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-be1607254b", "line_id": "L-a35ea997e2", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2313,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2456,11 +2346,11 @@
         <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2482,11 +2372,11 @@
         <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>295</v>
+        <v>347</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2501,23 +2391,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>133</v>
+        <v>-15</v>
       </c>
       <c r="E28" t="n">
-        <v>428</v>
+        <v>332</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0110", "receivable_term_quarters": 0, "revenue_wan": 133.0}</t>
+          <t>maintenance_expense | {"line_id": "L-a35ea997e2"}</t>
         </is>
       </c>
     </row>
@@ -2527,23 +2417,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a35ea997e2", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2443,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-5d0732565d", "line_id": "L-a35ea997e2", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a35ea997e2", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2579,23 +2469,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E31" t="n">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2612,11 +2502,11 @@
         <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2631,23 +2521,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-a35ea997e2"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2657,23 +2547,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a35ea997e2", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2683,23 +2573,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E35" t="n">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a35ea997e2", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2599,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="E36" t="n">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>maintenance_expense | {"line_id": "L-a35ea997e2"}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2625,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a35ea997e2", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2651,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a35ea997e2", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2787,23 +2677,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>-4</v>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0004", "receivable_term_quarters": 0, "revenue_wan": 80.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2813,23 +2703,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>329</v>
+        <v>239</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2839,23 +2729,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>313</v>
+        <v>225</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-07e42e954a", "line_id": "L-a35ea997e2", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2872,11 +2762,11 @@
         <v>-14</v>
       </c>
       <c r="E42" t="n">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2891,23 +2781,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E43" t="n">
-        <v>285</v>
+        <v>196</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-a35ea997e2"}</t>
         </is>
       </c>
     </row>
@@ -2917,23 +2807,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>270</v>
+        <v>196</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-a35ea997e2"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a35ea997e2", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2950,222 +2840,14 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>270</v>
+        <v>196</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a35ea997e2", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="n">
-        <v>43</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>270</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>第4年4季</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a35ea997e2", "asset_type": "production_line"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="n">
-        <v>44</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Pay_AD</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E47" t="n">
-        <v>266</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="n">
-        <v>45</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E48" t="n">
-        <v>252</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>46</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E49" t="n">
-        <v>238</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="n">
-        <v>47</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E50" t="n">
-        <v>224</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E51" t="n">
-        <v>209</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-a35ea997e2"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>209</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-a35ea997e2", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>209</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-a35ea997e2", "asset_type": "production_line"}</t>
         </is>
@@ -3562,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3587,10 +3269,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3612,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3662,10 +3344,10 @@
         <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>-22</v>
+        <v>-75</v>
       </c>
       <c r="G20" t="n">
-        <v>-55</v>
+        <v>-75</v>
       </c>
       <c r="H20" t="n">
         <v>-61</v>
@@ -3712,10 +3394,10 @@
         <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-37.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-70.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H22" t="n">
         <v>-76.2</v>
@@ -3762,10 +3444,10 @@
         <v>-100.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-37.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-70.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H24" t="n">
         <v>-76.2</v>
@@ -3812,10 +3494,10 @@
         <v>-100.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-37.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-70.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H26" t="n">
         <v>-76.2</v>
@@ -3911,13 +3593,13 @@
         <v>407</v>
       </c>
       <c r="F30" t="n">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="G30" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="H30" t="n">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31">
@@ -3986,13 +3668,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4036,13 +3718,13 @@
         <v>407</v>
       </c>
       <c r="F35" t="n">
-        <v>385</v>
+        <v>332</v>
       </c>
       <c r="G35" t="n">
-        <v>330</v>
+        <v>257</v>
       </c>
       <c r="H35" t="n">
-        <v>269</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36">
@@ -4161,13 +3843,13 @@
         <v>488.6</v>
       </c>
       <c r="F40" t="n">
-        <v>451.4</v>
+        <v>398.4</v>
       </c>
       <c r="G40" t="n">
-        <v>381.2</v>
+        <v>308.2</v>
       </c>
       <c r="H40" t="n">
-        <v>305</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41">
@@ -4339,10 +4021,10 @@
         <v>-186.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-223.6</v>
+        <v>-276.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-293.8</v>
+        <v>-366.8</v>
       </c>
     </row>
     <row r="48">
@@ -4361,10 +4043,10 @@
         <v>-100.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-37.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-70.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H48" t="n">
         <v>-76.2</v>
@@ -4386,13 +4068,13 @@
         <v>488.6</v>
       </c>
       <c r="F49" t="n">
-        <v>451.4</v>
+        <v>398.4</v>
       </c>
       <c r="G49" t="n">
-        <v>381.2</v>
+        <v>308.2</v>
       </c>
       <c r="H49" t="n">
-        <v>305</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50">
@@ -4411,13 +4093,13 @@
         <v>488.6</v>
       </c>
       <c r="F50" t="n">
-        <v>451.4</v>
+        <v>398.4</v>
       </c>
       <c r="G50" t="n">
-        <v>381.2</v>
+        <v>308.2</v>
       </c>
       <c r="H50" t="n">
-        <v>305</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
